--- a/test_files/BTG_P.ACCIONES_EEFF_2025-06-30.xlsx
+++ b/test_files/BTG_P.ACCIONES_EEFF_2025-06-30.xlsx
@@ -1,46 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyectos\03_iastronauts\test_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDriveUniversidad EIA\Documentos\Valen\BTG Pactual\Proyectos\iastronauts_creditiq\test_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6F5E94-1928-4E90-9F7C-E76F8CD0C7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC65A65F-45D7-40E8-8496-C0D7291A2E68}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Estado Situación Financiera" sheetId="1" r:id="rId1"/>
-    <sheet name="Estado Resultados" sheetId="2" r:id="rId2"/>
-    <sheet name="Cambios Activos Netos" sheetId="3" r:id="rId3"/>
-    <sheet name="Flujo de Efectivo" sheetId="4" r:id="rId4"/>
-    <sheet name="Jerarquia Valor Razonable" sheetId="5" r:id="rId5"/>
-    <sheet name="Activos Financieros VR" sheetId="6" r:id="rId6"/>
-    <sheet name="Pasivos Financieros" sheetId="7" r:id="rId7"/>
-    <sheet name="Partes Relacionadas" sheetId="8" r:id="rId8"/>
-    <sheet name="Gastos Relacionadas" sheetId="9" r:id="rId9"/>
-    <sheet name="Efectivo" sheetId="10" r:id="rId10"/>
-    <sheet name="Inversiones" sheetId="11" r:id="rId11"/>
-    <sheet name="Cuentas por Pagar" sheetId="12" r:id="rId12"/>
-    <sheet name="Activos Netos 2025" sheetId="13" r:id="rId13"/>
-    <sheet name="Activos Netos 2024" sheetId="14" r:id="rId14"/>
-    <sheet name="Ingresos Operacionales" sheetId="15" r:id="rId15"/>
-    <sheet name="Gastos Operacionales" sheetId="16" r:id="rId16"/>
-    <sheet name="Gastos Administrativos" sheetId="17" r:id="rId17"/>
-    <sheet name="Riesgo Mercado" sheetId="18" r:id="rId18"/>
+    <sheet name="BALANCE" sheetId="1" r:id="rId1"/>
+    <sheet name="ESTADO_RESULTADOS" sheetId="2" r:id="rId2"/>
+    <sheet name="ESTADO_CAMBIOS" sheetId="3" r:id="rId3"/>
+    <sheet name="FLUJO_EFECTIVO" sheetId="4" r:id="rId4"/>
+    <sheet name="VALOR_RAZONABLE_JERARQUIA" sheetId="5" r:id="rId5"/>
+    <sheet name="VALOR_RAZONABLE_ACTIVOS" sheetId="6" r:id="rId6"/>
+    <sheet name="VALOR_RAZONABLE_PASIVOS" sheetId="7" r:id="rId7"/>
+    <sheet name="PARTES_RELACIONADAS_ACTIVOS" sheetId="8" r:id="rId8"/>
+    <sheet name="PARTES_RELACIONADAS_PASIVOS" sheetId="19" r:id="rId9"/>
+    <sheet name="EFECTIVO" sheetId="10" r:id="rId10"/>
+    <sheet name="INSTRUMENTOS" sheetId="11" r:id="rId11"/>
+    <sheet name="CUENTAS_POR_PAGAR" sheetId="12" r:id="rId12"/>
+    <sheet name="ACTIVOS_NETOS_ACTUAL" sheetId="13" r:id="rId13"/>
+    <sheet name="ACTIVOS_NETOS_ANTERIOR" sheetId="14" r:id="rId14"/>
+    <sheet name="INGRESOS_OPE" sheetId="15" r:id="rId15"/>
+    <sheet name="GASTOS_OPE" sheetId="16" r:id="rId16"/>
+    <sheet name="GASTOS_ADM" sheetId="17" r:id="rId17"/>
+    <sheet name="RIESGOS" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="129">
-  <si>
-    <t>Estado Situación Financiera</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="131">
   <si>
     <t>Concepto</t>
   </si>
@@ -78,9 +75,6 @@
     <t>Total activo neto de inversionistas</t>
   </si>
   <si>
-    <t>Estado Resultados</t>
-  </si>
-  <si>
     <t>Jun 2025</t>
   </si>
   <si>
@@ -105,12 +99,6 @@
     <t>Gastos administrativos</t>
   </si>
   <si>
-    <t>Cambios Activos Netos</t>
-  </si>
-  <si>
-    <t>Junio 2024</t>
-  </si>
-  <si>
     <t>Activos netos iniciales</t>
   </si>
   <si>
@@ -123,9 +111,6 @@
     <t>Activos netos finales</t>
   </si>
   <si>
-    <t>Flujo de Efectivo</t>
-  </si>
-  <si>
     <t>Utilidad valoración inversiones</t>
   </si>
   <si>
@@ -153,24 +138,6 @@
     <t>Efectivo final</t>
   </si>
   <si>
-    <t>Jerarquia Valor Razonable</t>
-  </si>
-  <si>
-    <t>Instrumento</t>
-  </si>
-  <si>
-    <t>Nivel 1 2025</t>
-  </si>
-  <si>
-    <t>Nivel 2 2025</t>
-  </si>
-  <si>
-    <t>Nivel 1 2024</t>
-  </si>
-  <si>
-    <t>Nivel 2 2024</t>
-  </si>
-  <si>
     <t>Acciones Locales</t>
   </si>
   <si>
@@ -180,21 +147,9 @@
     <t>Total Instrumentos Patrimonio</t>
   </si>
   <si>
-    <t>Activos Financieros VR</t>
-  </si>
-  <si>
-    <t>Activo</t>
-  </si>
-  <si>
-    <t>VR 2025</t>
-  </si>
-  <si>
     <t>VL 2025</t>
   </si>
   <si>
-    <t>VR 2024</t>
-  </si>
-  <si>
     <t>VL 2024</t>
   </si>
   <si>
@@ -207,24 +162,9 @@
     <t>Pasivos Financieros</t>
   </si>
   <si>
-    <t>Pasivo</t>
-  </si>
-  <si>
     <t>Total pasivos financieros</t>
   </si>
   <si>
-    <t>Partes Relacionadas</t>
-  </si>
-  <si>
-    <t>Fondos de inversión administrados</t>
-  </si>
-  <si>
-    <t>Comisión administración por pagar</t>
-  </si>
-  <si>
-    <t>Gastos Relacionadas</t>
-  </si>
-  <si>
     <t>Comisión administración</t>
   </si>
   <si>
@@ -424,6 +364,72 @@
   </si>
   <si>
     <t>Total Activos Financieros</t>
+  </si>
+  <si>
+    <t>(No Auditado)</t>
+  </si>
+  <si>
+    <t>(Auditado)</t>
+  </si>
+  <si>
+    <t>JUNIO 2025</t>
+  </si>
+  <si>
+    <t>DICIEMBRE 2024</t>
+  </si>
+  <si>
+    <t>Acumulado</t>
+  </si>
+  <si>
+    <t>Trimestral</t>
+  </si>
+  <si>
+    <t>JUNIO DE 2025</t>
+  </si>
+  <si>
+    <t>JUNIO DE 2024</t>
+  </si>
+  <si>
+    <t>1 DE ABRIL AL 30 DE JUNIO DE 2025</t>
+  </si>
+  <si>
+    <t>1 DE ABRIL AL 30 DE JUNIO DE 2024</t>
+  </si>
+  <si>
+    <t>(No auditado)</t>
+  </si>
+  <si>
+    <t>DICIEMBRE DE 2024</t>
+  </si>
+  <si>
+    <t>Nivel 1</t>
+  </si>
+  <si>
+    <t>Nivel 2</t>
+  </si>
+  <si>
+    <t>DICIEMBRE DE 2025</t>
+  </si>
+  <si>
+    <t>Activos Financieros</t>
+  </si>
+  <si>
+    <t>Valor razonable</t>
+  </si>
+  <si>
+    <t>Valor en libros</t>
+  </si>
+  <si>
+    <t>Parte Relacionada</t>
+  </si>
+  <si>
+    <t>Operación</t>
+  </si>
+  <si>
+    <t>Fondos administrados por BTG Pactual S.A. Comisionista de Bolsa</t>
+  </si>
+  <si>
+    <t>Comisión de administración</t>
   </si>
 </sst>
 </file>
@@ -467,7 +473,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -489,8 +495,14 @@
         <fgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -522,11 +534,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -535,6 +584,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -542,7 +596,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -845,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
@@ -854,21 +929,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="A1" s="1"/>
+      <c r="B1" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="B3" s="3">
+        <v>262131</v>
+      </c>
+      <c r="C3" s="3">
+        <v>137183</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -876,10 +962,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="3">
-        <v>262131</v>
+        <v>39521260</v>
       </c>
       <c r="C4" s="3">
-        <v>137183</v>
+        <v>52559635</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -887,54 +973,54 @@
         <v>5</v>
       </c>
       <c r="B5" s="3">
-        <v>39521260</v>
+        <v>29986</v>
       </c>
       <c r="C5" s="3">
-        <v>52559635</v>
+        <v>7399</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3">
-        <v>29986</v>
-      </c>
-      <c r="C6" s="3">
-        <v>7399</v>
+      <c r="B6" s="5">
+        <v>39813377</v>
+      </c>
+      <c r="C6" s="5">
+        <v>52704217</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5">
-        <v>39813377</v>
-      </c>
-      <c r="C7" s="5">
-        <v>52704217</v>
+      <c r="B7" s="3">
+        <v>19447</v>
+      </c>
+      <c r="C7" s="3">
+        <v>9841</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="5">
         <v>19447</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>9841</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5">
-        <v>19447</v>
-      </c>
-      <c r="C9" s="5">
-        <v>9841</v>
+      <c r="B9" s="3">
+        <v>28034501</v>
+      </c>
+      <c r="C9" s="3">
+        <v>47306434</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -942,38 +1028,24 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>28034501</v>
+        <v>11759429</v>
       </c>
       <c r="C10" s="3">
-        <v>47306434</v>
+        <v>5387942</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3">
-        <v>11759429</v>
-      </c>
-      <c r="C11" s="3">
-        <v>5387942</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="5">
+      <c r="B11" s="5">
         <v>39793930</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C11" s="5">
         <v>52694376</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -990,33 +1062,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="A1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3">
         <v>192288</v>
@@ -1027,10 +1099,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C5" s="3">
         <v>56510</v>
@@ -1041,10 +1113,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3">
         <v>13333</v>
@@ -1055,7 +1127,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5">
@@ -1086,43 +1158,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="A1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
+      <c r="A2" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3">
         <v>327743</v>
@@ -1139,7 +1211,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B5" s="3">
         <v>256123</v>
@@ -1156,7 +1228,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B6" s="3">
         <v>2015701</v>
@@ -1173,7 +1245,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3">
         <v>1142005</v>
@@ -1190,7 +1262,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B8" s="3">
         <v>90143</v>
@@ -1207,7 +1279,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B9" s="3">
         <v>125523</v>
@@ -1224,7 +1296,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B10" s="3">
         <v>234673</v>
@@ -1241,7 +1313,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B11" s="3">
         <v>4960683</v>
@@ -1258,7 +1330,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B12" s="3">
         <v>46959</v>
@@ -1275,7 +1347,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B13" s="3">
         <v>224520</v>
@@ -1292,7 +1364,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B14" s="3">
         <v>0</v>
@@ -1309,7 +1381,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="5">
@@ -1340,26 +1412,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="A1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B4" s="3">
         <v>11855</v>
@@ -1370,7 +1442,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3">
         <v>7543</v>
@@ -1381,7 +1453,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3">
         <v>49</v>
@@ -1392,7 +1464,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B7" s="5">
         <v>19447</v>
@@ -1422,34 +1494,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="A1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B4" s="3">
         <v>22.28</v>
@@ -1466,7 +1538,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="B5" s="3">
         <v>37.79</v>
@@ -1483,7 +1555,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B6" s="3">
         <v>10.75</v>
@@ -1500,7 +1572,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B7" s="3">
         <v>13.6</v>
@@ -1517,7 +1589,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3">
         <v>21.6</v>
@@ -1534,7 +1606,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1564,34 +1636,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="A1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B4" s="3">
         <v>17.34</v>
@@ -1608,7 +1680,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B5" s="3">
         <v>16.690000000000001</v>
@@ -1625,7 +1697,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3">
         <v>14.39</v>
@@ -1642,7 +1714,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3">
         <v>29.49</v>
@@ -1659,7 +1731,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3">
         <v>10.59</v>
@@ -1676,7 +1748,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1703,34 +1775,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="A1" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B4" s="3">
         <v>8740138</v>
@@ -1747,7 +1819,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B5" s="3">
         <v>3214524</v>
@@ -1764,7 +1836,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="B6" s="3">
         <v>112099</v>
@@ -1781,7 +1853,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B7" s="3">
         <v>26854</v>
@@ -1798,7 +1870,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="B8" s="3">
         <v>5143</v>
@@ -1815,7 +1887,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="B9" s="3">
         <v>25</v>
@@ -1832,7 +1904,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="B10" s="3">
         <v>0</v>
@@ -1849,7 +1921,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3">
         <v>0</v>
@@ -1866,7 +1938,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B12" s="5">
         <v>12098783</v>
@@ -1899,34 +1971,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="A1" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B4" s="3">
         <v>29476</v>
@@ -1943,7 +2015,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="B5" s="3">
         <v>21300</v>
@@ -1960,7 +2032,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B6" s="5">
         <v>50776</v>
@@ -1993,34 +2065,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="A1" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
         <v>279082</v>
@@ -2037,7 +2109,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B5" s="3">
         <v>7839</v>
@@ -2054,7 +2126,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B6" s="3">
         <v>1332</v>
@@ -2071,7 +2143,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B7" s="3">
         <v>325</v>
@@ -2088,7 +2160,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
@@ -2105,7 +2177,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B9" s="5">
         <v>288578</v>
@@ -2141,34 +2213,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="A1" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
         <v>262131</v>
@@ -2185,7 +2257,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3">
         <v>39521260</v>
@@ -2202,7 +2274,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
         <v>29986</v>
@@ -2219,7 +2291,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3">
         <v>19447</v>
@@ -2244,128 +2316,154 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="5" width="15" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3">
-        <v>12098783</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2842206</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1928822</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1041929</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3">
-        <v>-50776</v>
+        <v>12098783</v>
       </c>
       <c r="C5" s="3">
-        <v>-22604</v>
+        <v>2842206</v>
       </c>
       <c r="D5" s="3">
-        <v>-24724</v>
+        <v>1928822</v>
       </c>
       <c r="E5" s="3">
-        <v>-12524</v>
+        <v>1041929</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B6" s="3">
-        <v>12048007</v>
+        <v>-50776</v>
       </c>
       <c r="C6" s="3">
-        <v>2819602</v>
+        <v>-22604</v>
       </c>
       <c r="D6" s="3">
-        <v>1904098</v>
+        <v>-24724</v>
       </c>
       <c r="E6" s="3">
-        <v>1029405</v>
+        <v>-12524</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3">
-        <v>-288578</v>
+        <v>12048007</v>
       </c>
       <c r="C7" s="3">
-        <v>-116413</v>
+        <v>2819602</v>
       </c>
       <c r="D7" s="3">
-        <v>-137595</v>
+        <v>1904098</v>
       </c>
       <c r="E7" s="3">
-        <v>-61731</v>
+        <v>1029405</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3">
+        <v>-288578</v>
+      </c>
+      <c r="C8" s="3">
+        <v>-116413</v>
+      </c>
+      <c r="D8" s="3">
+        <v>-137595</v>
+      </c>
+      <c r="E8" s="3">
+        <v>-61731</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
         <v>11759429</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C9" s="3">
         <v>2703189</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D9" s="3">
         <v>1766503</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E9" s="3">
         <v>967674</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2373,89 +2471,86 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+    <row r="1" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="16"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="3">
+        <v>52694376</v>
+      </c>
+      <c r="C3" s="3">
+        <v>10944771</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
-        <v>52694376</v>
+        <v>18914013</v>
       </c>
       <c r="C4" s="3">
-        <v>10944771</v>
+        <v>5586384</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3">
-        <v>18914013</v>
+        <v>-43573888</v>
       </c>
       <c r="C5" s="3">
-        <v>5586384</v>
+        <v>-3581454</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3">
-        <v>-43573888</v>
+        <v>11759429</v>
       </c>
       <c r="C6" s="3">
-        <v>-3581454</v>
+        <v>2703189</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B7" s="3">
-        <v>11759429</v>
+        <v>39793930</v>
       </c>
       <c r="C7" s="3">
-        <v>2703189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>39793930</v>
-      </c>
-      <c r="C8" s="3">
         <v>15652890</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2463,7 +2558,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -2471,158 +2566,155 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="16"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3">
+        <v>11759429</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2703189</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3">
-        <v>11759429</v>
+        <v>-8740138</v>
       </c>
       <c r="C4" s="3">
-        <v>2703189</v>
+        <v>-2011866</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3">
-        <v>-8740138</v>
+        <v>21778513</v>
       </c>
       <c r="C5" s="3">
-        <v>-2011866</v>
+        <v>-2512476</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3">
-        <v>21778513</v>
+        <v>-22587</v>
       </c>
       <c r="C6" s="3">
-        <v>-2512476</v>
+        <v>-157462</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B7" s="3">
-        <v>-22587</v>
+        <v>9606</v>
       </c>
       <c r="C7" s="3">
-        <v>-157462</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3">
-        <v>9606</v>
+        <v>24784823</v>
       </c>
       <c r="C8" s="3">
-        <v>589</v>
+        <v>-1978026</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3">
-        <v>24784823</v>
+        <v>18914013</v>
       </c>
       <c r="C9" s="3">
-        <v>-1978026</v>
+        <v>5586384</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3">
-        <v>18914013</v>
+        <v>-43573888</v>
       </c>
       <c r="C10" s="3">
-        <v>5586384</v>
+        <v>-3581454</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B11" s="3">
-        <v>-43573888</v>
+        <v>-24659875</v>
       </c>
       <c r="C11" s="3">
-        <v>-3581454</v>
+        <v>2004930</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B12" s="3">
-        <v>-24659875</v>
+        <v>124948</v>
       </c>
       <c r="C12" s="3">
-        <v>2004930</v>
+        <v>26904</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
-        <v>124948</v>
+        <v>137183</v>
       </c>
       <c r="C13" s="3">
-        <v>26904</v>
+        <v>144388</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B14" s="3">
-        <v>137183</v>
+        <v>262131</v>
       </c>
       <c r="C14" s="3">
-        <v>144388</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="3">
-        <v>262131</v>
-      </c>
-      <c r="C15" s="3">
         <v>171292</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2637,44 +2729,42 @@
     <col min="2" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="B2" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>38551195</v>
@@ -2691,7 +2781,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
@@ -2708,7 +2798,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B6" s="5">
         <v>38551195</v>
@@ -2724,8 +2814,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>128</v>
+      <c r="A7" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="B7" s="5">
         <v>38551195</v>
@@ -2742,16 +2832,17 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -2759,85 +2850,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="B1" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="13"/>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>52</v>
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="3">
+        <v>39521260</v>
+      </c>
+      <c r="C3" s="3">
+        <v>39521260</v>
+      </c>
+      <c r="D3" s="3">
+        <v>52559635</v>
+      </c>
+      <c r="E3" s="3">
+        <v>52559635</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>39521260</v>
+        <v>29986</v>
       </c>
       <c r="C4" s="3">
-        <v>39521260</v>
+        <v>29986</v>
       </c>
       <c r="D4" s="3">
-        <v>52559635</v>
+        <v>7399</v>
       </c>
       <c r="E4" s="3">
-        <v>52559635</v>
+        <v>7399</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3">
-        <v>29986</v>
-      </c>
-      <c r="C5" s="3">
-        <v>29986</v>
-      </c>
-      <c r="D5" s="3">
-        <v>7399</v>
-      </c>
-      <c r="E5" s="3">
-        <v>7399</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="5">
+      <c r="A5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="5">
         <v>39551246</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C5" s="5">
         <v>39551246</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D5" s="5">
         <v>52567034</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E5" s="5">
         <v>52567034</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2845,7 +2938,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -2853,68 +2946,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="B1" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="18"/>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>52</v>
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>19447</v>
+      </c>
+      <c r="C3" s="3">
+        <v>19447</v>
+      </c>
+      <c r="D3" s="3">
+        <v>9841</v>
+      </c>
+      <c r="E3" s="3">
+        <v>9841</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="5">
         <v>19447</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>19447</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="5">
         <v>9841</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="5">
         <v>9841</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="5">
-        <v>19447</v>
-      </c>
-      <c r="C5" s="5">
-        <v>19447</v>
-      </c>
-      <c r="D5" s="5">
-        <v>9841</v>
-      </c>
-      <c r="E5" s="5">
-        <v>9841</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2922,104 +3017,89 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="1" max="1" width="61" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3">
         <v>970065</v>
       </c>
-      <c r="C4" s="3">
+      <c r="D2" s="3">
         <v>272412</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="3">
-        <v>7543</v>
-      </c>
-      <c r="C5" s="3">
-        <v>9508</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49DFCBAC-6114-4896-9318-76C1824FE26B}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="38.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="59.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="38.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="3">
-        <v>279082</v>
-      </c>
-      <c r="C4" s="3">
-        <v>108076</v>
+    <row r="1" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" s="3">
+        <v>7543</v>
+      </c>
+      <c r="D2" s="3">
+        <v>9508</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>